--- a/Result/profitability/3317.xlsx
+++ b/Result/profitability/3317.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5812499999999999</v>
+        <v>0.5325</v>
       </c>
       <c r="N2" t="n">
-        <v>26.3975</v>
+        <v>26.435</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>0.475</v>
+        <v>0.5337499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>24.84875</v>
+        <v>25.04125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0.55</v>
+        <v>0.5475</v>
       </c>
       <c r="N4" t="n">
-        <v>23.5975</v>
+        <v>23.7025</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4475</v>
+        <v>0.4625</v>
       </c>
       <c r="N5" t="n">
-        <v>21.98</v>
+        <v>22.29875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.51</v>
       </c>
       <c r="M6" t="n">
-        <v>0.43625</v>
+        <v>0.4475</v>
       </c>
       <c r="N6" t="n">
-        <v>20.86625</v>
+        <v>21.0925</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>0.41625</v>
+        <v>0.5275</v>
       </c>
       <c r="N7" t="n">
-        <v>19.97</v>
+        <v>19.93625</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.07</v>
       </c>
       <c r="M8" t="n">
-        <v>0.57125</v>
+        <v>0.55625</v>
       </c>
       <c r="N8" t="n">
-        <v>19.21</v>
+        <v>19.14875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4812500000000001</v>
+        <v>0.48125</v>
       </c>
       <c r="N9" t="n">
         <v>17.91125</v>
@@ -1899,7 +1899,7 @@
         <v>0.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0.40375</v>
+        <v>0.4037499999999999</v>
       </c>
       <c r="N12" t="n">
         <v>18.42875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>726</v>
+      </c>
+      <c r="D75" t="n">
+        <v>517</v>
+      </c>
+      <c r="E75" t="n">
+        <v>210</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="G75" t="n">
+        <v>91</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.57%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>87</v>
+      </c>
+      <c r="K75" t="n">
+        <v>64</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.075</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.490000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.016695059625213</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.550000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09692132269099196</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
